--- a/ARTICLES.xlsx
+++ b/ARTICLES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Articles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Articles" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Articles'!$A$1:$G$669</definedName>
@@ -855,9 +855,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -890,9 +890,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -925,9 +925,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -960,9 +960,9 @@
           <t>Medium Breed</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1835,9 +1835,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -1870,9 +1870,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -1905,9 +1905,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -1940,9 +1940,9 @@
           <t>Large</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -2255,9 +2255,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -2290,9 +2290,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -2325,9 +2325,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2360,9 +2360,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -3095,9 +3095,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -3130,9 +3130,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -3165,9 +3165,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -3200,9 +3200,9 @@
           <t>Small Breed</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
@@ -4075,9 +4075,9 @@
           <t>Roundup</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G102" s="9" t="inlineStr">
@@ -4460,9 +4460,9 @@
           <t>Roundup</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G113" s="9" t="inlineStr">
@@ -5300,9 +5300,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -5335,9 +5335,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -5370,9 +5370,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -5405,9 +5405,9 @@
           <t>Small Breed</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
@@ -6280,9 +6280,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -6315,9 +6315,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -6350,9 +6350,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -6385,9 +6385,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -6700,9 +6700,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -6735,9 +6735,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -6770,9 +6770,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F179" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -6805,9 +6805,9 @@
           <t>Large</t>
         </is>
       </c>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
@@ -6840,9 +6840,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -6875,9 +6875,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -6910,9 +6910,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -6945,9 +6945,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -7680,9 +7680,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -7715,9 +7715,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -7750,9 +7750,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -7785,9 +7785,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
@@ -9185,9 +9185,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F248" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G248" s="4" t="inlineStr">
@@ -9220,9 +9220,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F249" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G249" s="4" t="inlineStr">
@@ -9255,9 +9255,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F250" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G250" s="4" t="inlineStr">
@@ -9290,9 +9290,9 @@
           <t>Giant</t>
         </is>
       </c>
-      <c r="F251" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F251" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G251" s="6" t="inlineStr">
@@ -10620,9 +10620,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F289" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F289" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr">
@@ -10655,9 +10655,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F290" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F290" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G290" s="4" t="inlineStr">
@@ -10690,9 +10690,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F291" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F291" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G291" s="4" t="inlineStr">
@@ -10725,9 +10725,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F292" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F292" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G292" s="6" t="inlineStr">
@@ -11180,9 +11180,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F305" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F305" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G305" s="4" t="inlineStr">
@@ -11215,9 +11215,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F306" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F306" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G306" s="4" t="inlineStr">
@@ -11250,9 +11250,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F307" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F307" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G307" s="4" t="inlineStr">
@@ -11285,9 +11285,9 @@
           <t>Large Breed</t>
         </is>
       </c>
-      <c r="F308" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F308" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G308" s="6" t="inlineStr">
@@ -11915,9 +11915,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F326" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F326" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G326" s="4" t="inlineStr">
@@ -11950,9 +11950,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F327" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F327" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G327" s="4" t="inlineStr">
@@ -11985,9 +11985,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F328" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F328" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G328" s="4" t="inlineStr">
@@ -12020,9 +12020,9 @@
           <t>Giant Breed</t>
         </is>
       </c>
-      <c r="F329" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F329" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G329" s="6" t="inlineStr">
@@ -12895,9 +12895,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F354" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F354" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G354" s="4" t="inlineStr">
@@ -12930,9 +12930,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F355" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F355" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -12965,9 +12965,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F356" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F356" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G356" s="4" t="inlineStr">
@@ -13000,9 +13000,9 @@
           <t>Medium Breed</t>
         </is>
       </c>
-      <c r="F357" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F357" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G357" s="6" t="inlineStr">
@@ -13735,9 +13735,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F378" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F378" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G378" s="4" t="inlineStr">
@@ -13770,9 +13770,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F379" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F379" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G379" s="4" t="inlineStr">
@@ -13805,9 +13805,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F380" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F380" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G380" s="4" t="inlineStr">
@@ -13840,9 +13840,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F381" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F381" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G381" s="6" t="inlineStr">
@@ -14295,9 +14295,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F394" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F394" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G394" s="4" t="inlineStr">
@@ -14330,9 +14330,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F395" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F395" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G395" s="4" t="inlineStr">
@@ -14365,9 +14365,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F396" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F396" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G396" s="4" t="inlineStr">
@@ -14400,9 +14400,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F397" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F397" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G397" s="6" t="inlineStr">
@@ -14435,9 +14435,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F398" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F398" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G398" s="4" t="inlineStr">
@@ -14470,9 +14470,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F399" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F399" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -14505,9 +14505,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F400" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F400" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G400" s="4" t="inlineStr">
@@ -14540,9 +14540,9 @@
           <t>Giant Breed</t>
         </is>
       </c>
-      <c r="F401" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F401" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G401" s="6" t="inlineStr">
@@ -15345,9 +15345,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F424" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F424" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G424" s="4" t="inlineStr">
@@ -15380,9 +15380,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F425" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F425" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G425" s="4" t="inlineStr">
@@ -15415,9 +15415,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F426" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F426" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G426" s="4" t="inlineStr">
@@ -15450,9 +15450,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F427" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F427" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G427" s="6" t="inlineStr">
@@ -16045,9 +16045,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F444" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F444" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G444" s="4" t="inlineStr">
@@ -16080,9 +16080,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F445" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F445" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G445" s="4" t="inlineStr">
@@ -16115,9 +16115,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F446" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F446" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G446" s="4" t="inlineStr">
@@ -16150,9 +16150,9 @@
           <t>Giant Breed</t>
         </is>
       </c>
-      <c r="F447" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F447" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G447" s="6" t="inlineStr">
@@ -17305,9 +17305,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F480" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F480" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G480" s="4" t="inlineStr">
@@ -17340,9 +17340,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F481" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F481" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G481" s="4" t="inlineStr">
@@ -17375,9 +17375,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F482" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F482" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G482" s="4" t="inlineStr">
@@ -17410,9 +17410,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F483" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F483" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G483" s="6" t="inlineStr">
@@ -19195,9 +19195,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F534" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F534" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G534" s="4" t="inlineStr">
@@ -19230,9 +19230,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F535" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F535" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G535" s="4" t="inlineStr">
@@ -19265,9 +19265,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F536" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F536" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G536" s="4" t="inlineStr">
@@ -19300,9 +19300,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F537" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-28 00:00 BJT</t>
+      <c r="F537" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G537" s="6" t="inlineStr">
@@ -20035,9 +20035,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F558" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F558" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G558" s="4" t="inlineStr">
@@ -20070,9 +20070,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F559" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F559" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G559" s="4" t="inlineStr">
@@ -20105,9 +20105,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F560" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F560" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G560" s="4" t="inlineStr">
@@ -20140,9 +20140,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F561" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-29 00:00 BJT</t>
+      <c r="F561" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G561" s="6" t="inlineStr">
@@ -21715,9 +21715,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F606" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F606" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G606" s="4" t="inlineStr">
@@ -21750,9 +21750,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F607" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F607" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G607" s="4" t="inlineStr">
@@ -21785,9 +21785,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F608" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F608" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G608" s="4" t="inlineStr">
@@ -21820,9 +21820,9 @@
           <t>Medium Breed</t>
         </is>
       </c>
-      <c r="F609" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F609" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G609" s="6" t="inlineStr">
@@ -21995,9 +21995,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F614" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F614" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G614" s="4" t="inlineStr">
@@ -22030,9 +22030,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F615" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F615" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G615" s="4" t="inlineStr">
@@ -22065,9 +22065,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F616" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F616" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G616" s="4" t="inlineStr">
@@ -22100,9 +22100,9 @@
           <t>Giant</t>
         </is>
       </c>
-      <c r="F617" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-27 00:00 BJT</t>
+      <c r="F617" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G617" s="6" t="inlineStr">

--- a/ARTICLES.xlsx
+++ b/ARTICLES.xlsx
@@ -1275,9 +1275,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1310,9 +1310,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1345,9 +1345,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1380,9 +1380,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -7820,9 +7820,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F209" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -7855,9 +7855,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F210" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -7890,9 +7890,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F211" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -7925,9 +7925,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F212" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G212" s="6" t="inlineStr">
@@ -8520,9 +8520,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F229" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -8555,9 +8555,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -8590,9 +8590,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F231" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -8625,9 +8625,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F232" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G232" s="6" t="inlineStr">
@@ -13455,9 +13455,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F370" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F370" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G370" s="4" t="inlineStr">
@@ -13490,9 +13490,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F371" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F371" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G371" s="4" t="inlineStr">
@@ -13525,9 +13525,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F372" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F372" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G372" s="4" t="inlineStr">
@@ -13560,9 +13560,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F373" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F373" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G373" s="6" t="inlineStr">
@@ -15485,9 +15485,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F428" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F428" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G428" s="4" t="inlineStr">
@@ -15520,9 +15520,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F429" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F429" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G429" s="4" t="inlineStr">
@@ -15555,9 +15555,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F430" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F430" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G430" s="4" t="inlineStr">
@@ -15590,9 +15590,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F431" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F431" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G431" s="6" t="inlineStr">
@@ -17165,9 +17165,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F476" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F476" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G476" s="4" t="inlineStr">
@@ -17200,9 +17200,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F477" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F477" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G477" s="4" t="inlineStr">
@@ -17235,9 +17235,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F478" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F478" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G478" s="4" t="inlineStr">
@@ -17270,9 +17270,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F479" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F479" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G479" s="6" t="inlineStr">
@@ -17445,9 +17445,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F484" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F484" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G484" s="4" t="inlineStr">
@@ -17480,9 +17480,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F485" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F485" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G485" s="4" t="inlineStr">
@@ -17515,9 +17515,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F486" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F486" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G486" s="4" t="inlineStr">
@@ -17550,9 +17550,9 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="F487" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-04-30 00:00 BJT</t>
+      <c r="F487" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G487" s="6" t="inlineStr">

--- a/ARTICLES.xlsx
+++ b/ARTICLES.xlsx
@@ -3769,7 +3769,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Bernedoodle First Year Costs</t>
+          <t>Bernedoodle Cost Year 1: $5,200–$10,500 (Real Budget)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Cane Corso First-Year Costs: Full Budget Breakdown</t>
+          <t>Cane Corso Cost Year 1: $4,450–$11,500 Budget Breakdown</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Cavalier King Charles Spaniel First-Year Costs</t>
+          <t>Cavalier King Charles Spaniel Cost Year 1: $2,000–$3,500</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>Miniature Poodle First-Year Costs</t>
+          <t>Miniature Poodle Cost Year 1: $1,800–$3,200 (Real Budget)</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>Shih Tzu First-Year Costs</t>
+          <t>Shih Tzu Cost Year 1: $2,500–$5,000 (Real Budget)</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>Tibetan Mastiff First Year Costs</t>
+          <t>Tibetan Mastiff Cost Year 1: $5,000–$8,500 (Real Budget)</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
@@ -24697,7 +24697,7 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>Tibetan Spaniel First Year Costs</t>
+          <t>Tibetan Spaniel Cost Year 1: $1,200–$2,200 (Real Budget)</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
@@ -25117,7 +25117,7 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>Vizsla First-Year Costs: Full Budget Breakdown</t>
+          <t>Vizsla Cost Year 1: $2,700–$6,100 Budget Breakdown</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
@@ -25887,7 +25887,7 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>Whippet First-Year Costs</t>
+          <t>Whippet Cost Year 1: $1,500–$3,000 (Real Budget)</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>Wire Fox Terrier First Year Costs</t>
+          <t>Wire Fox Terrier Cost Year 1: $1,500–$2,500 (Real Budget)</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">

--- a/ARTICLES.xlsx
+++ b/ARTICLES.xlsx
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Alaskan Malamute Grooming Guide: Coat Care and Shedding Management</t>
+          <t>Alaskan Malamute Grooming: Every 6–8 Weeks + Shedding Plan</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Anatolian Shepherd Dog Grooming Guide</t>
+          <t>Anatolian Shepherd Grooming: Brush Daily + Trim Every 6–8 Weeks</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Australian Shepherd Grooming Guide</t>
+          <t>Australian Shepherd Grooming: Brush 2–3x/Week + Pro Tools</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Belgian Malinois Grooming Guide</t>
+          <t>Belgian Malinois Grooming: Every 6–8 Weeks + Shedding Plan</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Dachshund Grooming Guide</t>
+          <t>Dachshund Grooming Guide: Smooth, Long, and Wire Coat Care</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Gordon Setter Grooming Guide</t>
+          <t>Gordon Setter Grooming: Every 4–6 Weeks for the Feathered Coat</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="B515" s="2" t="inlineStr">
         <is>
-          <t>Newfoundland Grooming Guide</t>
+          <t>Newfoundland Grooming: Every 4–6 Weeks (Heavy Coat Schedule)</t>
         </is>
       </c>
       <c r="C515" s="2" t="inlineStr">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="B552" s="2" t="inlineStr">
         <is>
-          <t>Pekingese Grooming Guide</t>
+          <t>Pekingese Grooming Guide: Every 4–6 Weeks for the Long Coat</t>
         </is>
       </c>
       <c r="C552" s="2" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="B576" s="2" t="inlineStr">
         <is>
-          <t>Portuguese Water Dog Grooming Guide: Curly Coat Care and Trims</t>
+          <t>Portuguese Water Dog Grooming: Every 6–8 Weeks (Curly Coat)</t>
         </is>
       </c>
       <c r="C576" s="2" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>Wire Fox Terrier Grooming Guide</t>
+          <t>Wire Fox Terrier Grooming: Hand-Strip Every 8–10 Weeks</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">

--- a/ARTICLES.xlsx
+++ b/ARTICLES.xlsx
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>Black Dog Breeds</t>
+          <t>Black Dog Breeds: 10 Beautiful All-Black Breeds Explained</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B203" s="7" t="inlineStr">
         <is>
-          <t>Calmest Dog Breeds</t>
+          <t>Calmest Dog Breeds: 10 Laid-Back Breeds for Quiet Homes</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="B244" s="7" t="inlineStr">
         <is>
-          <t>Chinese Dog Breeds</t>
+          <t>Chinese Dog Breeds: 10 Ancient Breeds From China Explained</t>
         </is>
       </c>
       <c r="C244" s="7" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="B269" s="7" t="inlineStr">
         <is>
-          <t>Curly-Haired Dog Breeds</t>
+          <t>Curly-Haired Dog Breeds: 10 Breeds With Tight Curls or Waves</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="B325" s="7" t="inlineStr">
         <is>
-          <t>Fluffy Dog Breeds</t>
+          <t>Fluffy Dog Breeds: 10 Cloud-Like Breeds You Will Want to Hug</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="B330" s="7" t="inlineStr">
         <is>
-          <t>Friendliest Dog Breeds</t>
+          <t>Friendliest Dog Breeds: 10 Top Social Breeds for Families</t>
         </is>
       </c>
       <c r="C330" s="7" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="B331" s="7" t="inlineStr">
         <is>
-          <t>German Dog Breeds</t>
+          <t>German Dog Breeds: 10 Native Breeds From Germany Explained</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="B349" s="7" t="inlineStr">
         <is>
-          <t>Giant Dog Breeds</t>
+          <t>Giant Dog Breeds: 10 of the World's Largest Dog Breeds</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="B394" s="7" t="inlineStr">
         <is>
-          <t>Healthiest Dog Breeds</t>
+          <t>Healthiest Dog Breeds: 10 Long-Lived and Hardy Breeds</t>
         </is>
       </c>
       <c r="C394" s="7" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="B403" s="7" t="inlineStr">
         <is>
-          <t>Irish Dog Breeds</t>
+          <t>Irish Dog Breeds: 9 Native Breeds of Ireland Explained</t>
         </is>
       </c>
       <c r="C403" s="7" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="B428" s="7" t="inlineStr">
         <is>
-          <t>Japanese Dog Breeds</t>
+          <t>Japanese Dog Breeds: The 6 Native Nihon Ken Explained</t>
         </is>
       </c>
       <c r="C428" s="7" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="B466" s="7" t="inlineStr">
         <is>
-          <t>Long-Haired Dog Breeds</t>
+          <t>Long-Haired Dog Breeds: 10 Elegant Flowing-Coat Breeds</t>
         </is>
       </c>
       <c r="C466" s="7" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="B483" s="7" t="inlineStr">
         <is>
-          <t>Medium-Sized Dog Breeds</t>
+          <t>Medium-Sized Dog Breeds: 10 Best 30 to 60 Pound Dogs</t>
         </is>
       </c>
       <c r="C483" s="7" t="inlineStr">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="B648" s="7" t="inlineStr">
         <is>
-          <t>Short-Haired Dog Breeds</t>
+          <t>Short-Haired Dog Breeds: 10 Low-Shedding Smooth-Coat Breeds</t>
         </is>
       </c>
       <c r="C648" s="7" t="inlineStr">
@@ -26027,7 +26027,7 @@
       </c>
       <c r="B732" s="7" t="inlineStr">
         <is>
-          <t>White Dog Breeds</t>
+          <t>White Dog Breeds: 10 Pure-White Breeds You Will Love</t>
         </is>
       </c>
       <c r="C732" s="7" t="inlineStr">

--- a/ARTICLES.xlsx
+++ b/ARTICLES.xlsx
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Alaskan Malamute Puppy Checklist: What to Do Before and After Bringing One Home</t>
+          <t>Alaskan Malamute Puppy Checklist: First 90 Days</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Aussiedoodle Grooming Guide: Coat Care, Brushing Schedules, and Professional Trim Frequency</t>
+          <t>Aussiedoodle Grooming Guide: Coat Care &amp; Trim</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Bernedoodle Grooming Guide: Coat Care, Brushing Schedules, and Professional Trim Frequency</t>
+          <t>Bernedoodle Grooming Guide: Coat Care &amp; Trim</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Boston Terrier Puppy Checklist: What to Do Before and After Bringing One Home</t>
+          <t>Boston Terrier Puppy Checklist: First 90 Days</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>Can Dogs Eat Butternut Squash? A Nutritious Addition to Your Dog's Diet</t>
+          <t>Can Dogs Eat Butternut Squash? Yes &amp; Why</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Cane Corso Puppy Checklist: Everything to Do Before and After Bringing One Home</t>
+          <t>Cane Corso Puppy Checklist: First 90 Days at Home</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Cavapoo Grooming Guide: Coat Care, Brushing Schedules, and Professional Trim Frequency</t>
+          <t>Cavapoo Grooming Guide: Coat Care &amp; Trim Schedule</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>English Springer Spaniel Puppy Checklist: Everything to Do Before Bringing One Home</t>
+          <t>English Springer Spaniel Puppy Checklist: 90 Days</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Goldendoodle Grooming Guide: Coat Care, Brushing Schedules, and Professional Trim Frequency</t>
+          <t>Goldendoodle Grooming Guide: Coat Care &amp; Trim</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Havanese Puppy Checklist: What to Do Before and After Bringing One Home</t>
+          <t>Havanese Puppy Checklist: First 90 Days at Home</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Italian Greyhound Puppy Checklist: What to Do Before and After Bringing One Home</t>
+          <t>Italian Greyhound Puppy Checklist: First 90 Days</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>Labradoodle Grooming Guide: Coat Care, Brushing Schedules, and Professional Trim Frequency</t>
+          <t>Labradoodle Grooming Guide: Coat Care &amp; Trim</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="B593" s="2" t="inlineStr">
         <is>
-          <t>Pomeranian Puppy Checklist: What to Do Before and After Bringing One Home</t>
+          <t>Pomeranian Puppy Checklist: First 90 Days at Home</t>
         </is>
       </c>
       <c r="C593" s="2" t="inlineStr">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="B597" s="2" t="inlineStr">
         <is>
-          <t>Portuguese Water Dog Puppy Checklist: What to Do Before and After Bringing One Home</t>
+          <t>Portuguese Water Dog Puppy Checklist: 90 Days</t>
         </is>
       </c>
       <c r="C597" s="2" t="inlineStr">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="B652" s="2" t="inlineStr">
         <is>
-          <t>Sheepadoodle Grooming Guide: Coat Care, Brushing Schedules, and Professional Trim Frequency</t>
+          <t>Sheepadoodle Grooming Guide: Coat Care &amp; Trim</t>
         </is>
       </c>
       <c r="C652" s="2" t="inlineStr">
@@ -24677,7 +24677,7 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>Standard Poodle Grooming Guide: Curly Coat Care and Professional Trim Schedules</t>
+          <t>Standard Poodle Grooming Guide: Curly Coat Care</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
@@ -25727,7 +25727,7 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>Vizsla Puppy Checklist: Everything to Do Before and After Bringing One Home</t>
+          <t>Vizsla Puppy Checklist: First 90 Days at Home</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
@@ -25937,7 +25937,7 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>Weimaraner Puppy Checklist: What to Do Before and After Bringing One Home</t>
+          <t>Weimaraner Puppy Checklist: First 90 Days at Home</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
@@ -27119,7 +27119,7 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire Terrier Puppy Checklist: What to Do Before and After Bringing One Home</t>
+          <t>Yorkshire Terrier Puppy Checklist: 90 Days</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">

--- a/ARTICLES.xlsx
+++ b/ARTICLES.xlsx
@@ -7781,7 +7781,7 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>Can Dogs Eat Butternut Squash? Yes &amp; Why</t>
+          <t>Can Dogs Eat Butternut Squash? Yes — Benefits &amp; How to Serve</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>Can Dogs Have Sunflower Seeds? Safety &amp; Benefits</t>
+          <t>Can Dogs Have Sunflower Seeds? Benefits, Risks &amp; Safe Amounts</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Cavapoo Costs: First Year Budget Guide</t>
+          <t>Cavapoo Price: Puppy Cost &amp; First-Year Budget</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="B527" s="7" t="inlineStr">
         <is>
-          <t>Most Loyal Dog Breeds</t>
+          <t>10 Most Loyal Dog Breeds</t>
         </is>
       </c>
       <c r="C527" s="7" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="B551" s="2" t="inlineStr">
         <is>
-          <t>Nova Scotia Duck Tolling Retriever Cost: $3,000–$6,500 Year 1</t>
+          <t>Nova Scotia Duck Tolling Retriever Price &amp; First-Year Costs</t>
         </is>
       </c>
       <c r="C551" s="2" t="inlineStr">

--- a/ARTICLES.xlsx
+++ b/ARTICLES.xlsx
@@ -44,7 +44,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,11 +76,6 @@
         <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -108,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,9 +127,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6700,9 +6692,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-06-22 20:00 BJT</t>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G177" s="6" t="inlineStr">
@@ -8865,7 +8857,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Cavalier King Charles Spaniel Cost Year 1: $2,000–$3,500</t>
+          <t>Cavalier King Charles Spaniel Cost: $2,000-$3,500 First Year</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -11193,9 +11185,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F312" s="9" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-06-22 20:00 BJT</t>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G312" s="6" t="inlineStr">
@@ -26768,9 +26760,9 @@
           <t>Guide</t>
         </is>
       </c>
-      <c r="F757" s="9" t="inlineStr">
-        <is>
-          <t>Scheduled 2026-06-22 20:00 BJT</t>
+      <c r="F757" s="3" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G757" s="6" t="inlineStr">
